--- a/documentation/Time Plan.xlsx
+++ b/documentation/Time Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://collyer82-my.sharepoint.com/personal/25cookeg899_collyers_ac_uk/Documents/01 - Computer Science/Python Projects/Theatre-Booking/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F67DFED9-50B2-4CEA-83FB-C3254BC2F593}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3CDFC6B-1B1B-48B0-898B-2FDF5C8F19A5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3072" yWindow="3072" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Time Plan: Design and Develop a Theatre Booking System</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>UML (Pseudocode)</t>
+  </si>
+  <si>
+    <t>Week Ending</t>
   </si>
 </sst>
 </file>
@@ -314,9 +317,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -329,14 +329,17 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -357,6 +360,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -637,21 +644,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="11"/>
+      <c r="A2" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="B2" s="6">
         <v>46080</v>
       </c>
@@ -695,45 +704,45 @@
       <c r="J3" s="10"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
       <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -751,16 +760,16 @@
       <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
     </row>
@@ -768,13 +777,13 @@
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
     </row>
@@ -782,13 +791,13 @@
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
     </row>
@@ -796,13 +805,13 @@
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
     </row>
@@ -810,13 +819,13 @@
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
@@ -824,13 +833,13 @@
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
     </row>
@@ -849,18 +858,18 @@
       <c r="J14" s="10"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
@@ -868,13 +877,13 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
@@ -883,26 +892,26 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="15"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="14"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="15"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="14"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -919,60 +928,60 @@
       <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="22"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="19"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="23"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="20"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="23"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="20"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="23"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
@@ -986,7 +995,7 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="23"/>
+      <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
@@ -1000,7 +1009,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="23"/>
+      <c r="J25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1013,6 +1022,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="10d644ba-cf16-43e8-a31a-a6f565d9c224">
+      <UserInfo>
+        <DisplayName>Helen Browne</DisplayName>
+        <AccountId>773</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="10d644ba-cf16-43e8-a31a-a6f565d9c224" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B31D159F86750749BAD869CB65D39E6C" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b52437f09c885264a74a7224ddae0bf2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94" xmlns:ns3="10d644ba-cf16-43e8-a31a-a6f565d9c224" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5a7cbcd1702d69c471f1439a09cbaf55" ns2:_="" ns3:_="">
     <xsd:import namespace="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94"/>
@@ -1267,34 +1303,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AAEB363-E0B7-4846-BB2E-A880D29866B2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="10d644ba-cf16-43e8-a31a-a6f565d9c224"/>
+    <ds:schemaRef ds:uri="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="10d644ba-cf16-43e8-a31a-a6f565d9c224">
-      <UserInfo>
-        <DisplayName>Helen Browne</DisplayName>
-        <AccountId>773</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="10d644ba-cf16-43e8-a31a-a6f565d9c224" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D154ECB-7BD7-4B38-A220-236438B72B0E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1311,23 +1339,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AAEB363-E0B7-4846-BB2E-A880D29866B2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="10d644ba-cf16-43e8-a31a-a6f565d9c224"/>
-    <ds:schemaRef ds:uri="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/documentation/Time Plan.xlsx
+++ b/documentation/Time Plan.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://collyer82-my.sharepoint.com/personal/25cookeg899_collyers_ac_uk/Documents/01 - Computer Science/Python Projects/Theatre-Booking/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3CDFC6B-1B1B-48B0-898B-2FDF5C8F19A5}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F2A6218-E0E3-407B-9DEB-85CBB69B14D7}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3072" yWindow="3072" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_Toc2601324" localSheetId="0">Sheet1!$A$7</definedName>
-    <definedName name="_Toc2601331" localSheetId="0">Sheet1!$A$16</definedName>
-    <definedName name="_Toc2601332" localSheetId="0">Sheet1!$A$17</definedName>
+    <definedName name="_Toc2601331" localSheetId="0">Sheet1!$A$17</definedName>
+    <definedName name="_Toc2601332" localSheetId="0">Sheet1!$A$18</definedName>
     <definedName name="_Toc2601333" localSheetId="0">Sheet1!#REF!</definedName>
     <definedName name="_Toc2601334" localSheetId="0">Sheet1!#REF!</definedName>
   </definedNames>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>Time Plan: Design and Develop a Theatre Booking System</t>
   </si>
@@ -66,9 +66,6 @@
     <t>Breaking the system into sub problems</t>
   </si>
   <si>
-    <t>Task List for each sub problem</t>
-  </si>
-  <si>
     <t>Algorithms for each sub problem</t>
   </si>
   <si>
@@ -115,6 +112,12 @@
   </si>
   <si>
     <t>Week Ending</t>
+  </si>
+  <si>
+    <t>Design overview</t>
+  </si>
+  <si>
+    <t>UI Designs</t>
   </si>
 </sst>
 </file>
@@ -174,7 +177,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -217,6 +220,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -295,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -331,15 +346,18 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -632,7 +650,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="77.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -644,22 +662,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
-        <v>23</v>
+      <c r="A2" s="21" t="s">
+        <v>22</v>
       </c>
       <c r="B2" s="6">
         <v>46080</v>
@@ -707,7 +725,7 @@
       <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="19"/>
+      <c r="B4" s="26"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
@@ -721,7 +739,7 @@
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="20"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
@@ -735,7 +753,7 @@
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="20"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
@@ -761,7 +779,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="14"/>
@@ -774,41 +792,41 @@
       <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="20"/>
+      <c r="A9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="24"/>
       <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="A10" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="17"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="25"/>
       <c r="C11" s="20"/>
       <c r="D11" s="14"/>
-      <c r="E11" s="16"/>
+      <c r="E11" s="14"/>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
@@ -817,9 +835,9 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="14"/>
+        <v>8</v>
+      </c>
+      <c r="B12" s="17"/>
       <c r="C12" s="20"/>
       <c r="D12" s="14"/>
       <c r="E12" s="16"/>
@@ -831,12 +849,12 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="20"/>
       <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="E13" s="16"/>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
@@ -844,120 +862,120 @@
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
       <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
+      <c r="I17" s="14"/>
       <c r="J17" s="14"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
-        <v>15</v>
+      <c r="A18" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="17"/>
+      <c r="E18" s="14"/>
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
+      <c r="H18" s="20"/>
       <c r="I18" s="20"/>
       <c r="J18" s="14"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="19"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="20"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="19"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -971,7 +989,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
@@ -985,16 +1003,16 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
       <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -1011,10 +1029,24 @@
       <c r="I25" s="4"/>
       <c r="J25" s="20"/>
     </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="20"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A16:J16"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="66" orientation="landscape" r:id="rId1"/>
@@ -1040,15 +1072,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B31D159F86750749BAD869CB65D39E6C" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b52437f09c885264a74a7224ddae0bf2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94" xmlns:ns3="10d644ba-cf16-43e8-a31a-a6f565d9c224" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5a7cbcd1702d69c471f1439a09cbaf55" ns2:_="" ns3:_="">
     <xsd:import namespace="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94"/>
@@ -1303,6 +1326,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AAEB363-E0B7-4846-BB2E-A880D29866B2}">
   <ds:schemaRefs>
@@ -1315,14 +1347,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D154ECB-7BD7-4B38-A220-236438B72B0E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1339,4 +1363,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/documentation/Time Plan.xlsx
+++ b/documentation/Time Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://collyer82-my.sharepoint.com/personal/25cookeg899_collyers_ac_uk/Documents/01 - Computer Science/Python Projects/Theatre-Booking/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F2A6218-E0E3-407B-9DEB-85CBB69B14D7}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43DACDBE-70AE-418A-972A-6559EA16C7E6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_Toc2601324" localSheetId="0">Sheet1!$A$7</definedName>
-    <definedName name="_Toc2601331" localSheetId="0">Sheet1!$A$17</definedName>
-    <definedName name="_Toc2601332" localSheetId="0">Sheet1!$A$18</definedName>
+    <definedName name="_Toc2601331" localSheetId="0">Sheet1!$A$18</definedName>
+    <definedName name="_Toc2601332" localSheetId="0">Sheet1!$A$19</definedName>
     <definedName name="_Toc2601333" localSheetId="0">Sheet1!#REF!</definedName>
     <definedName name="_Toc2601334" localSheetId="0">Sheet1!#REF!</definedName>
   </definedNames>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>Time Plan: Design and Develop a Theatre Booking System</t>
   </si>
@@ -118,6 +118,12 @@
   </si>
   <si>
     <t>UI Designs</t>
+  </si>
+  <si>
+    <t>Database designs</t>
+  </si>
+  <si>
+    <t>Overrun</t>
   </si>
 </sst>
 </file>
@@ -177,7 +183,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,6 +235,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -310,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -319,12 +331,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -338,26 +348,63 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -650,7 +697,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="77.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -662,391 +709,409 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>46080</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>46087</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <v>46094</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>46101</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>46108</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>45033</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>45040</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <v>45047</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="5">
         <v>45054</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="7"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="24"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="4"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="13"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="24"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="4"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="26"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="24"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+      <c r="A11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
+        <v>8</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="15"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="14"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="15"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="19"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
       <c r="J22" s="20"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="20"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="14"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="20"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="14"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="20"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="14"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="20"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:J17"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="66" orientation="landscape" r:id="rId1"/>
@@ -1072,6 +1137,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B31D159F86750749BAD869CB65D39E6C" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b52437f09c885264a74a7224ddae0bf2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94" xmlns:ns3="10d644ba-cf16-43e8-a31a-a6f565d9c224" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5a7cbcd1702d69c471f1439a09cbaf55" ns2:_="" ns3:_="">
     <xsd:import namespace="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94"/>
@@ -1326,15 +1400,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AAEB363-E0B7-4846-BB2E-A880D29866B2}">
   <ds:schemaRefs>
@@ -1347,6 +1412,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D154ECB-7BD7-4B38-A220-236438B72B0E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1363,12 +1436,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/documentation/Time Plan.xlsx
+++ b/documentation/Time Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://collyer82-my.sharepoint.com/personal/25cookeg899_collyers_ac_uk/Documents/01 - Computer Science/Python Projects/Theatre-Booking/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43DACDBE-70AE-418A-972A-6559EA16C7E6}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5179BFAD-C074-46F8-BF89-6D7B3EA12844}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_Toc2601324" localSheetId="0">Sheet1!$A$7</definedName>
-    <definedName name="_Toc2601331" localSheetId="0">Sheet1!$A$18</definedName>
-    <definedName name="_Toc2601332" localSheetId="0">Sheet1!$A$19</definedName>
+    <definedName name="_Toc2601331" localSheetId="0">Sheet1!$A$19</definedName>
+    <definedName name="_Toc2601332" localSheetId="0">Sheet1!$A$20</definedName>
     <definedName name="_Toc2601333" localSheetId="0">Sheet1!#REF!</definedName>
     <definedName name="_Toc2601334" localSheetId="0">Sheet1!#REF!</definedName>
   </definedNames>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>Time Plan: Design and Develop a Theatre Booking System</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t>Overrun</t>
+  </si>
+  <si>
+    <t>Inputs and outputs</t>
   </si>
 </sst>
 </file>
@@ -697,7 +700,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="77.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -928,12 +931,12 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="24"/>
       <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
+      <c r="E15" s="27"/>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
       <c r="H15" s="15"/>
@@ -941,120 +944,120 @@
       <c r="J15" s="13"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="29" t="s">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
       <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
+      <c r="I19" s="15"/>
       <c r="J19" s="15"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
-        <v>14</v>
+      <c r="A20" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
-      <c r="E20" s="16"/>
+      <c r="E20" s="15"/>
       <c r="F20" s="15"/>
       <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
+      <c r="H20" s="14"/>
       <c r="I20" s="14"/>
       <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="15"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="20"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="14"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -1068,7 +1071,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -1082,21 +1085,21 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
       <c r="J26" s="14"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -1108,10 +1111,24 @@
       <c r="I27" s="13"/>
       <c r="J27" s="14"/>
     </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="14"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:J18"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="66" orientation="landscape" r:id="rId1"/>
@@ -1137,15 +1154,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B31D159F86750749BAD869CB65D39E6C" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b52437f09c885264a74a7224ddae0bf2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94" xmlns:ns3="10d644ba-cf16-43e8-a31a-a6f565d9c224" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5a7cbcd1702d69c471f1439a09cbaf55" ns2:_="" ns3:_="">
     <xsd:import namespace="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94"/>
@@ -1400,6 +1408,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AAEB363-E0B7-4846-BB2E-A880D29866B2}">
   <ds:schemaRefs>
@@ -1412,14 +1429,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D154ECB-7BD7-4B38-A220-236438B72B0E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1436,4 +1445,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/documentation/Time Plan.xlsx
+++ b/documentation/Time Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://collyer82-my.sharepoint.com/personal/25cookeg899_collyers_ac_uk/Documents/01 - Computer Science/Python Projects/Theatre-Booking/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5179BFAD-C074-46F8-BF89-6D7B3EA12844}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC314E1B-3D14-4D33-B544-DD9482764C10}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_Toc2601324" localSheetId="0">Sheet1!$A$7</definedName>
-    <definedName name="_Toc2601331" localSheetId="0">Sheet1!$A$19</definedName>
-    <definedName name="_Toc2601332" localSheetId="0">Sheet1!$A$20</definedName>
+    <definedName name="_Toc2601331" localSheetId="0">Sheet1!$A$21</definedName>
+    <definedName name="_Toc2601332" localSheetId="0">Sheet1!$A$22</definedName>
     <definedName name="_Toc2601333" localSheetId="0">Sheet1!#REF!</definedName>
     <definedName name="_Toc2601334" localSheetId="0">Sheet1!#REF!</definedName>
   </definedNames>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>Time Plan: Design and Develop a Theatre Booking System</t>
   </si>
@@ -127,6 +127,15 @@
   </si>
   <si>
     <t>Inputs and outputs</t>
+  </si>
+  <si>
+    <t>Backend</t>
+  </si>
+  <si>
+    <t>Front End</t>
+  </si>
+  <si>
+    <t>Early</t>
   </si>
 </sst>
 </file>
@@ -186,7 +195,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -244,6 +253,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -325,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -407,6 +422,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -428,10 +455,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -700,7 +723,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="77.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -972,120 +995,124 @@
       <c r="J17" s="12"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="30"/>
+      <c r="C18" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="32"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="B21" s="13"/>
+      <c r="C21" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="15"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="15"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="15"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="20"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="14"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="14"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -1099,36 +1126,64 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
       <c r="J27" s="14"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
       <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A20:J20"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="66" orientation="landscape" r:id="rId1"/>
@@ -1154,6 +1209,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B31D159F86750749BAD869CB65D39E6C" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b52437f09c885264a74a7224ddae0bf2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94" xmlns:ns3="10d644ba-cf16-43e8-a31a-a6f565d9c224" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5a7cbcd1702d69c471f1439a09cbaf55" ns2:_="" ns3:_="">
     <xsd:import namespace="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94"/>
@@ -1408,15 +1472,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AAEB363-E0B7-4846-BB2E-A880D29866B2}">
   <ds:schemaRefs>
@@ -1429,6 +1484,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D154ECB-7BD7-4B38-A220-236438B72B0E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1445,12 +1508,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/documentation/Time Plan.xlsx
+++ b/documentation/Time Plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://collyer82-my.sharepoint.com/personal/25cookeg899_collyers_ac_uk/Documents/01 - Computer Science/Python Projects/Theatre-Booking/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC314E1B-3D14-4D33-B544-DD9482764C10}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5C34284-5E28-4EF5-82BE-A7058F6B0C1B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -340,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -417,23 +417,26 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -455,6 +458,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -735,18 +742,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -995,58 +1002,58 @@
       <c r="J17" s="12"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="33" t="s">
+      <c r="B18" s="28"/>
+      <c r="C18" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="32"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="13"/>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="14"/>
+      <c r="D21" s="24"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
@@ -1191,33 +1198,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="10d644ba-cf16-43e8-a31a-a6f565d9c224">
-      <UserInfo>
-        <DisplayName>Helen Browne</DisplayName>
-        <AccountId>773</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="10d644ba-cf16-43e8-a31a-a6f565d9c224" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B31D159F86750749BAD869CB65D39E6C" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b52437f09c885264a74a7224ddae0bf2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94" xmlns:ns3="10d644ba-cf16-43e8-a31a-a6f565d9c224" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5a7cbcd1702d69c471f1439a09cbaf55" ns2:_="" ns3:_="">
     <xsd:import namespace="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94"/>
@@ -1472,26 +1452,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AAEB363-E0B7-4846-BB2E-A880D29866B2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="10d644ba-cf16-43e8-a31a-a6f565d9c224"/>
-    <ds:schemaRef ds:uri="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="10d644ba-cf16-43e8-a31a-a6f565d9c224">
+      <UserInfo>
+        <DisplayName>Helen Browne</DisplayName>
+        <AccountId>773</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="10d644ba-cf16-43e8-a31a-a6f565d9c224" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D154ECB-7BD7-4B38-A220-236438B72B0E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1508,4 +1496,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AAEB363-E0B7-4846-BB2E-A880D29866B2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="10d644ba-cf16-43e8-a31a-a6f565d9c224"/>
+    <ds:schemaRef ds:uri="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/documentation/Time Plan.xlsx
+++ b/documentation/Time Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://collyer82-my.sharepoint.com/personal/25cookeg899_collyers_ac_uk/Documents/01 - Computer Science/Python Projects/Theatre-Booking/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5C34284-5E28-4EF5-82BE-A7058F6B0C1B}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5F05437-D146-4B3A-8312-E0686CD9494F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>Time Plan: Design and Develop a Theatre Booking System</t>
   </si>
@@ -340,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -436,6 +436,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1023,7 +1026,9 @@
       </c>
       <c r="B19" s="28"/>
       <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
+      <c r="D19" s="35" t="s">
+        <v>30</v>
+      </c>
       <c r="E19" s="30"/>
       <c r="F19" s="30"/>
       <c r="G19" s="30"/>

--- a/documentation/Time Plan.xlsx
+++ b/documentation/Time Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://collyer82-my.sharepoint.com/personal/25cookeg899_collyers_ac_uk/Documents/01 - Computer Science/Python Projects/Theatre-Booking/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5F05437-D146-4B3A-8312-E0686CD9494F}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08951E6D-F1D8-4181-B20D-877F9B39DBB8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1029,7 +1029,7 @@
       <c r="D19" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="30"/>
+      <c r="E19" s="34"/>
       <c r="F19" s="30"/>
       <c r="G19" s="30"/>
       <c r="H19" s="28"/>
@@ -1059,7 +1059,7 @@
         <v>30</v>
       </c>
       <c r="D21" s="24"/>
-      <c r="E21" s="14"/>
+      <c r="E21" s="24"/>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>

--- a/documentation/Time Plan.xlsx
+++ b/documentation/Time Plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://collyer82-my.sharepoint.com/personal/25cookeg899_collyers_ac_uk/Documents/01 - Computer Science/Python Projects/Theatre-Booking/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08951E6D-F1D8-4181-B20D-877F9B39DBB8}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="8_{2D523807-7404-4E18-A3A7-2E609803194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9435552-50C7-4384-B42D-7A4FF7A91C1E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>Time Plan: Design and Develop a Theatre Booking System</t>
   </si>
@@ -423,22 +423,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -461,10 +461,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -745,18 +741,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -1009,10 +1005,10 @@
         <v>28</v>
       </c>
       <c r="B18" s="28"/>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="34"/>
+      <c r="D18" s="31"/>
       <c r="E18" s="28"/>
       <c r="F18" s="28"/>
       <c r="G18" s="28"/>
@@ -1026,43 +1022,45 @@
       </c>
       <c r="B19" s="28"/>
       <c r="C19" s="28"/>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="28"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="35" t="s">
+        <v>26</v>
+      </c>
       <c r="I19" s="28"/>
       <c r="J19" s="28"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="13"/>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="30" t="s">
         <v>30</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
     </row>
@@ -1458,15 +1456,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="10d644ba-cf16-43e8-a31a-a6f565d9c224">
@@ -1482,6 +1471,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1504,14 +1502,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AAEB363-E0B7-4846-BB2E-A880D29866B2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1520,4 +1510,12 @@
     <ds:schemaRef ds:uri="9f27979c-cb1a-4f8c-bada-64f9d3ac4d94"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5823592-756B-4A38-BF13-8C42D4724CD5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>